--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-consent.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-consent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI &amp; EHDS Consent Profile</t>
+    <t>EU AI Consent and Processing Context</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A profile on the Consent resource to capture GDPR legal basis and EHDS secondary use opt-out.</t>
+    <t>A Consent profile documenting patient-facing information, permission status, and opt-out preferences for AI-supported processing where applicable.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1115,12 +1115,6 @@
   </si>
   <si>
     <t>When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActReason"/&gt;
-  &lt;code value="RESCH"/&gt;
-&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
@@ -6261,7 +6255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>302</v>
       </c>
@@ -6274,13 +6268,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -7739,7 +7733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>344</v>
       </c>
@@ -7752,13 +7746,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -7787,7 +7781,7 @@
         <v>18</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>348</v>
+        <v>18</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>18</v>
@@ -7805,10 +7799,10 @@
         <v>323</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -7855,10 +7849,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7884,13 +7878,13 @@
         <v>338</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7916,14 +7910,14 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y56" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y56" t="s" s="2">
+      <c r="Z56" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
       </c>
@@ -7940,7 +7934,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7969,10 +7963,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7998,13 +7992,13 @@
         <v>338</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8033,11 +8027,11 @@
         <v>323</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8054,7 +8048,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8083,10 +8077,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8112,10 +8106,10 @@
         <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8145,11 +8139,11 @@
         <v>176</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8166,7 +8160,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8195,10 +8189,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8224,13 +8218,13 @@
         <v>197</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8280,7 +8274,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8309,10 +8303,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8338,10 +8332,10 @@
         <v>236</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8349,7 +8343,7 @@
         <v>18</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>18</v>
@@ -8394,7 +8388,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8423,10 +8417,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8535,10 +8529,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8649,10 +8643,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8765,10 +8759,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8794,10 +8788,10 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8827,11 +8821,11 @@
         <v>111</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
       </c>
@@ -8848,7 +8842,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -8877,10 +8871,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8906,10 +8900,10 @@
         <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8960,7 +8954,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -8989,10 +8983,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9015,16 +9009,16 @@
         <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9074,7 +9068,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9103,10 +9097,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9132,10 +9126,10 @@
         <v>77</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9186,7 +9180,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
